--- a/artfynd/A 4645-2026 artfynd.xlsx
+++ b/artfynd/A 4645-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131527254</v>
       </c>
       <c r="B2" t="n">
-        <v>97882</v>
+        <v>97885</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>131527311</v>
       </c>
       <c r="B3" t="n">
-        <v>58047</v>
+        <v>58050</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>131527406</v>
       </c>
       <c r="B4" t="n">
-        <v>96253</v>
+        <v>96256</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 4645-2026 artfynd.xlsx
+++ b/artfynd/A 4645-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131527254</v>
       </c>
       <c r="B2" t="n">
-        <v>97885</v>
+        <v>97886</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>131527311</v>
       </c>
       <c r="B3" t="n">
-        <v>58050</v>
+        <v>58051</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>131527406</v>
       </c>
       <c r="B4" t="n">
-        <v>96256</v>
+        <v>96257</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 4645-2026 artfynd.xlsx
+++ b/artfynd/A 4645-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131527254</v>
       </c>
       <c r="B2" t="n">
-        <v>97886</v>
+        <v>97892</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>131527311</v>
       </c>
       <c r="B3" t="n">
-        <v>58051</v>
+        <v>58057</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>131527406</v>
       </c>
       <c r="B4" t="n">
-        <v>96257</v>
+        <v>96263</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 4645-2026 artfynd.xlsx
+++ b/artfynd/A 4645-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131527254</v>
       </c>
       <c r="B2" t="n">
-        <v>97892</v>
+        <v>97893</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>131527406</v>
       </c>
       <c r="B4" t="n">
-        <v>96263</v>
+        <v>96264</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 4645-2026 artfynd.xlsx
+++ b/artfynd/A 4645-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131527254</v>
       </c>
       <c r="B2" t="n">
-        <v>97893</v>
+        <v>97894</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>131527311</v>
       </c>
       <c r="B3" t="n">
-        <v>58057</v>
+        <v>58058</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>131527406</v>
       </c>
       <c r="B4" t="n">
-        <v>96264</v>
+        <v>96265</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 4645-2026 artfynd.xlsx
+++ b/artfynd/A 4645-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131527254</v>
       </c>
       <c r="B2" t="n">
-        <v>97894</v>
+        <v>97897</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>131527311</v>
       </c>
       <c r="B3" t="n">
-        <v>58058</v>
+        <v>58061</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>131527406</v>
       </c>
       <c r="B4" t="n">
-        <v>96265</v>
+        <v>96268</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 4645-2026 artfynd.xlsx
+++ b/artfynd/A 4645-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131527254</v>
       </c>
       <c r="B2" t="n">
-        <v>97897</v>
+        <v>97903</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>131527311</v>
       </c>
       <c r="B3" t="n">
-        <v>58061</v>
+        <v>58063</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>131527406</v>
       </c>
       <c r="B4" t="n">
-        <v>96268</v>
+        <v>96274</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 4645-2026 artfynd.xlsx
+++ b/artfynd/A 4645-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131527254</v>
       </c>
       <c r="B2" t="n">
-        <v>97903</v>
+        <v>97906</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>131527311</v>
       </c>
       <c r="B3" t="n">
-        <v>58063</v>
+        <v>58066</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>131527406</v>
       </c>
       <c r="B4" t="n">
-        <v>96274</v>
+        <v>96277</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 4645-2026 artfynd.xlsx
+++ b/artfynd/A 4645-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131527254</v>
       </c>
       <c r="B2" t="n">
-        <v>97906</v>
+        <v>97911</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>131527311</v>
       </c>
       <c r="B3" t="n">
-        <v>58066</v>
+        <v>58071</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>131527406</v>
       </c>
       <c r="B4" t="n">
-        <v>96277</v>
+        <v>96282</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 4645-2026 artfynd.xlsx
+++ b/artfynd/A 4645-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131527254</v>
+        <v>131527406</v>
       </c>
       <c r="B2" t="n">
-        <v>97913</v>
+        <v>96348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,19 +686,23 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221944</v>
+        <v>2810</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Rhytidiadelphus loreus</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
@@ -714,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>311081</v>
+        <v>311091</v>
       </c>
       <c r="R2" t="n">
-        <v>6544950</v>
+        <v>6544865</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -790,7 +794,7 @@
         <v>131527311</v>
       </c>
       <c r="B3" t="n">
-        <v>58073</v>
+        <v>58114</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,10 +920,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131527406</v>
+        <v>131527254</v>
       </c>
       <c r="B4" t="n">
-        <v>96284</v>
+        <v>97977</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -927,23 +931,19 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2810</v>
+        <v>221944</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Hedw.) Warnst.</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
@@ -959,10 +959,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>311091</v>
+        <v>311081</v>
       </c>
       <c r="R4" t="n">
-        <v>6544865</v>
+        <v>6544950</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 4645-2026 artfynd.xlsx
+++ b/artfynd/A 4645-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131527406</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -917,6 +927,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131527311</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1029,8 +1044,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131527254</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>